--- a/equipment_maintenance_forms/013_hydraulic_system_monitoring_log_form--equipment_maintenance_forms.xlsx
+++ b/equipment_maintenance_forms/013_hydraulic_system_monitoring_log_form--equipment_maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'equipment_type',_'label':_'type',_'type':_'select_one',_'options':_[{'name':_'hydraulic-equipment',_'label':_'hydraulic'},_{'name':_'pneumatic-equipment',_'label':_'pneumatic'}],_'required':_true}</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'equipment_type', 'label': 'Type', 'type': 'select_one', 'options': [{'name': 'hydraulic-equipment', 'label': 'Hydraulic'}, {'name': 'pneumatic-equipment', 'label': 'Pneumatic'}], 'required': True}</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'equipment_id',_'label':_'equipment_id',_'type':_'select_multiple',_'options':_[]}</t>
+          <t>equipment_id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'equipment_id', 'label': 'Equipment ID', 'type': 'select_multiple', 'options': []}</t>
+          <t>Equipment ID</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'equipment_serial_number',_'label':_'equipment_serial_number',_'type':_'text',_'options':_[]}</t>
+          <t>equipment_serial_number</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'equipment_serial_number', 'label': 'Equipment Serial Number', 'type': 'text', 'options': []}</t>
+          <t>Equipment Serial Number</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'equipment_model',_'label':_'equipment_model',_'type':_'text',_'options':_[]}</t>
+          <t>equipment_model</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'equipment_model', 'label': 'Equipment Model', 'type': 'text', 'options': []}</t>
+          <t>Equipment Model</t>
         </is>
       </c>
     </row>
